--- a/WWI modell.xlsx
+++ b/WWI modell.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/augusthodt/Desktop/Aksjemodellering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB9E52C8-40C6-2841-9B14-6FBE146D49F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0DB24BB-BE42-C146-8D36-9063ED670046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25200" yWindow="500" windowWidth="25880" windowHeight="26500" activeTab="1" xr2:uid="{5AE0DF26-B7DD-1242-A60E-253C73A930AF}"/>
   </bookViews>
@@ -118,7 +118,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="206">
   <si>
     <t>Kapitalstruktur</t>
   </si>
@@ -724,6 +724,18 @@
   </si>
   <si>
     <t>EBITDA Margin</t>
+  </si>
+  <si>
+    <t>0,8 NAV</t>
+  </si>
+  <si>
+    <t>% to 0,8</t>
+  </si>
+  <si>
+    <t>0,7 NAV</t>
+  </si>
+  <si>
+    <t>% to 0,7</t>
   </si>
 </sst>
 </file>
@@ -737,7 +749,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.0\ %"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -835,12 +847,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -972,7 +978,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1074,6 +1080,7 @@
     <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2810,88 +2817,88 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D6FABC2-1253-924E-8CB2-F0C03750A097}">
   <dimension ref="A2:H26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="7" width="10.83203125" style="2"/>
     <col min="8" max="8" width="12.83203125" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="44" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="H3" s="1" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="H4" s="2" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="H5" s="2" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="H6" s="2" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="H7" s="2" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="H8" s="2" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="H9" s="47" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="H10" s="47" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="H11" s="2" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="H12" s="2" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="H13" s="2" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="H14" s="2" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="44" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="44" t="s">
         <v>150</v>
       </c>
@@ -2905,7 +2912,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A9D41D6-FA1C-5144-915F-9569A5873643}">
   <dimension ref="A1:EQ97"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="4"/>
@@ -2929,7 +2936,7 @@
     <col min="46" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42">
+    <row r="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
       <c r="F1" s="7"/>
@@ -2944,7 +2951,7 @@
       <c r="O1" s="7"/>
       <c r="AB1" s="1"/>
     </row>
-    <row r="3" spans="1:42">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -3064,12 +3071,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:42">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="4">
-        <v>844</v>
+        <v>943</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>40</v>
@@ -3190,7 +3197,7 @@
         <v>1809.0577798239558</v>
       </c>
     </row>
-    <row r="5" spans="1:42">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
@@ -3307,13 +3314,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B6" s="5">
         <f>B4*B5</f>
-        <v>37625.519999999997</v>
+        <v>42038.939999999995</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -3460,7 +3467,7 @@
         <v>1809.0577798239558</v>
       </c>
     </row>
-    <row r="7" spans="1:42">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>37</v>
       </c>
@@ -3585,7 +3592,7 @@
         <v>-597.79096121702366</v>
       </c>
     </row>
-    <row r="8" spans="1:42">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>38</v>
       </c>
@@ -3710,13 +3717,13 @@
         <v>-663.2633045884121</v>
       </c>
     </row>
-    <row r="9" spans="1:42">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B9" s="6">
         <f>B6-B7+B8</f>
-        <v>37653.089999999997</v>
+        <v>42066.509999999995</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>46</v>
@@ -3836,7 +3843,7 @@
         <v>-244.80963173649536</v>
       </c>
     </row>
-    <row r="10" spans="1:42">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.25">
       <c r="C10" s="2" t="s">
         <v>47</v>
       </c>
@@ -3955,7 +3962,7 @@
         <v>-113.86494499371884</v>
       </c>
     </row>
-    <row r="11" spans="1:42">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>57</v>
       </c>
@@ -4107,7 +4114,7 @@
         <v>189.32893728830595</v>
       </c>
     </row>
-    <row r="12" spans="1:42">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.25">
       <c r="C12" s="2" t="s">
         <v>49</v>
       </c>
@@ -4226,13 +4233,13 @@
         <v>364.04833564861292</v>
       </c>
     </row>
-    <row r="13" spans="1:42">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>123</v>
       </c>
       <c r="B13" s="83">
         <f>SOTP!B4</f>
-        <v>0.59774246807432097</v>
+        <v>0.6420850589426671</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>50</v>
@@ -4343,7 +4350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:42">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="84"/>
       <c r="C14" s="2" t="s">
@@ -4455,13 +4462,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:42">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>199</v>
       </c>
       <c r="B15" s="83">
         <f>B6/(U46*B11)</f>
-        <v>1.0943975762737304</v>
+        <v>1.2227688559551275</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>52</v>
@@ -4572,7 +4579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:42">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.25">
       <c r="C16" s="2" t="s">
         <v>53</v>
       </c>
@@ -4718,7 +4725,14 @@
         <v>553.37727293691887</v>
       </c>
     </row>
-    <row r="17" spans="2:147">
+    <row r="17" spans="1:147" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B17" s="4">
+        <f>SOTP!G26*0.8</f>
+        <v>1174.9222155118887</v>
+      </c>
       <c r="C17" s="2" t="s">
         <v>54</v>
       </c>
@@ -4838,7 +4852,7 @@
         <v>-27.668863646845946</v>
       </c>
     </row>
-    <row r="18" spans="2:147">
+    <row r="18" spans="1:147" x14ac:dyDescent="0.25">
       <c r="C18" s="1" t="s">
         <v>55</v>
       </c>
@@ -5405,7 +5419,14 @@
         <v>182.99547750464887</v>
       </c>
     </row>
-    <row r="19" spans="2:147">
+    <row r="19" spans="1:147" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B19" s="85">
+        <f>(B17-B4)/B17</f>
+        <v>0.19739367632166618</v>
+      </c>
       <c r="C19" s="2" t="s">
         <v>86</v>
       </c>
@@ -5544,7 +5565,7 @@
         <v>114.26905531675206</v>
       </c>
     </row>
-    <row r="20" spans="2:147">
+    <row r="20" spans="1:147" x14ac:dyDescent="0.25">
       <c r="C20" s="2" t="s">
         <v>56</v>
       </c>
@@ -5685,7 +5706,14 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="21" spans="2:147">
+    <row r="21" spans="1:147" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B21" s="4">
+        <f>SOTP!G26*0.7</f>
+        <v>1028.0569385729025</v>
+      </c>
       <c r="AR21" s="2" t="s">
         <v>125</v>
       </c>
@@ -5693,7 +5721,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="22" spans="2:147">
+    <row r="22" spans="1:147" x14ac:dyDescent="0.25">
       <c r="C22" s="1" t="s">
         <v>29</v>
       </c>
@@ -5829,7 +5857,14 @@
         <v>59767.388262975772</v>
       </c>
     </row>
-    <row r="23" spans="2:147">
+    <row r="23" spans="1:147" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B23" s="23">
+        <f>(B21-B4)/B4</f>
+        <v>9.0198238147298493E-2</v>
+      </c>
       <c r="C23" s="2" t="s">
         <v>30</v>
       </c>
@@ -5984,7 +6019,7 @@
         <v>44.58</v>
       </c>
     </row>
-    <row r="24" spans="2:147">
+    <row r="24" spans="1:147" x14ac:dyDescent="0.25">
       <c r="D24" s="21"/>
       <c r="E24" s="21"/>
       <c r="F24" s="21"/>
@@ -6031,7 +6066,7 @@
         <v>1340.6771705467872</v>
       </c>
     </row>
-    <row r="25" spans="2:147">
+    <row r="25" spans="1:147" x14ac:dyDescent="0.25">
       <c r="C25" s="2" t="s">
         <v>130</v>
       </c>
@@ -6115,10 +6150,10 @@
       </c>
       <c r="AS25" s="36">
         <f>(AS24-B4)/B4</f>
-        <v>0.58848005988955832</v>
-      </c>
-    </row>
-    <row r="26" spans="2:147" s="61" customFormat="1">
+        <v>0.42171492104643399</v>
+      </c>
+    </row>
+    <row r="26" spans="1:147" s="61" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B26" s="82"/>
       <c r="C26" s="61" t="s">
         <v>201</v>
@@ -6225,7 +6260,7 @@
       </c>
       <c r="AG26" s="82"/>
     </row>
-    <row r="27" spans="2:147">
+    <row r="27" spans="1:147" x14ac:dyDescent="0.25">
       <c r="C27" s="2" t="s">
         <v>200</v>
       </c>
@@ -6290,7 +6325,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="29" spans="2:147">
+    <row r="29" spans="1:147" x14ac:dyDescent="0.25">
       <c r="C29" s="3" t="s">
         <v>113</v>
       </c>
@@ -6319,7 +6354,7 @@
       <c r="AA29" s="1"/>
       <c r="AB29" s="1"/>
     </row>
-    <row r="30" spans="2:147">
+    <row r="30" spans="1:147" x14ac:dyDescent="0.25">
       <c r="C30" s="2" t="s">
         <v>87</v>
       </c>
@@ -6406,7 +6441,7 @@
       <c r="AH30" s="13"/>
       <c r="AI30" s="13"/>
     </row>
-    <row r="31" spans="2:147">
+    <row r="31" spans="1:147" x14ac:dyDescent="0.25">
       <c r="C31" s="2" t="s">
         <v>88</v>
       </c>
@@ -6496,7 +6531,7 @@
       <c r="AH31" s="13"/>
       <c r="AI31" s="13"/>
     </row>
-    <row r="32" spans="2:147">
+    <row r="32" spans="1:147" x14ac:dyDescent="0.25">
       <c r="C32" s="2" t="s">
         <v>89</v>
       </c>
@@ -6583,7 +6618,7 @@
       <c r="AH32" s="13"/>
       <c r="AI32" s="13"/>
     </row>
-    <row r="33" spans="3:35">
+    <row r="33" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C33" s="2" t="s">
         <v>90</v>
       </c>
@@ -6670,7 +6705,7 @@
       <c r="AH33" s="13"/>
       <c r="AI33" s="13"/>
     </row>
-    <row r="34" spans="3:35">
+    <row r="34" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C34" s="2" t="s">
         <v>167</v>
       </c>
@@ -6757,7 +6792,7 @@
       <c r="AH34" s="13"/>
       <c r="AI34" s="13"/>
     </row>
-    <row r="35" spans="3:35">
+    <row r="35" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C35" s="2" t="s">
         <v>91</v>
       </c>
@@ -6844,7 +6879,7 @@
       <c r="AH35" s="13"/>
       <c r="AI35" s="13"/>
     </row>
-    <row r="36" spans="3:35">
+    <row r="36" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C36" s="2" t="s">
         <v>92</v>
       </c>
@@ -6931,7 +6966,7 @@
       <c r="AH36" s="13"/>
       <c r="AI36" s="13"/>
     </row>
-    <row r="37" spans="3:35">
+    <row r="37" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C37" s="2" t="s">
         <v>93</v>
       </c>
@@ -7018,7 +7053,7 @@
       <c r="AH37" s="13"/>
       <c r="AI37" s="13"/>
     </row>
-    <row r="38" spans="3:35">
+    <row r="38" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C38" s="2" t="s">
         <v>94</v>
       </c>
@@ -7105,7 +7140,7 @@
       <c r="AH38" s="13"/>
       <c r="AI38" s="13"/>
     </row>
-    <row r="39" spans="3:35">
+    <row r="39" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C39" s="2" t="s">
         <v>95</v>
       </c>
@@ -7192,7 +7227,7 @@
       <c r="AH39" s="13"/>
       <c r="AI39" s="13"/>
     </row>
-    <row r="40" spans="3:35">
+    <row r="40" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C40" s="2" t="s">
         <v>96</v>
       </c>
@@ -7279,7 +7314,7 @@
       <c r="AH40" s="13"/>
       <c r="AI40" s="13"/>
     </row>
-    <row r="41" spans="3:35">
+    <row r="41" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C41" s="1" t="s">
         <v>97</v>
       </c>
@@ -7391,7 +7426,7 @@
       <c r="AH41" s="13"/>
       <c r="AI41" s="13"/>
     </row>
-    <row r="42" spans="3:35">
+    <row r="42" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C42" s="2" t="s">
         <v>98</v>
       </c>
@@ -7478,7 +7513,7 @@
       <c r="AH42" s="13"/>
       <c r="AI42" s="13"/>
     </row>
-    <row r="43" spans="3:35">
+    <row r="43" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C43" s="2" t="s">
         <v>99</v>
       </c>
@@ -7565,7 +7600,7 @@
       <c r="AH43" s="13"/>
       <c r="AI43" s="13"/>
     </row>
-    <row r="44" spans="3:35">
+    <row r="44" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C44" s="2" t="s">
         <v>100</v>
       </c>
@@ -7652,7 +7687,7 @@
       <c r="AH44" s="13"/>
       <c r="AI44" s="13"/>
     </row>
-    <row r="45" spans="3:35">
+    <row r="45" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C45" s="2" t="s">
         <v>101</v>
       </c>
@@ -7739,7 +7774,7 @@
       <c r="AH45" s="13"/>
       <c r="AI45" s="13"/>
     </row>
-    <row r="46" spans="3:35">
+    <row r="46" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C46" s="11" t="s">
         <v>102</v>
       </c>
@@ -7851,7 +7886,7 @@
       <c r="AH46" s="13"/>
       <c r="AI46" s="13"/>
     </row>
-    <row r="47" spans="3:35">
+    <row r="47" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C47" s="2" t="s">
         <v>103</v>
       </c>
@@ -7938,7 +7973,7 @@
       <c r="AH47" s="13"/>
       <c r="AI47" s="13"/>
     </row>
-    <row r="48" spans="3:35">
+    <row r="48" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C48" s="2" t="s">
         <v>87</v>
       </c>
@@ -8025,7 +8060,7 @@
       <c r="AH48" s="13"/>
       <c r="AI48" s="13"/>
     </row>
-    <row r="49" spans="3:35">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C49" s="2" t="s">
         <v>115</v>
       </c>
@@ -8112,7 +8147,7 @@
       <c r="AH49" s="13"/>
       <c r="AI49" s="13"/>
     </row>
-    <row r="50" spans="3:35">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C50" s="2" t="s">
         <v>104</v>
       </c>
@@ -8199,7 +8234,7 @@
       <c r="AH50" s="13"/>
       <c r="AI50" s="13"/>
     </row>
-    <row r="51" spans="3:35">
+    <row r="51" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C51" s="2" t="s">
         <v>105</v>
       </c>
@@ -8286,7 +8321,7 @@
       <c r="AH51" s="13"/>
       <c r="AI51" s="13"/>
     </row>
-    <row r="52" spans="3:35">
+    <row r="52" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C52" s="2" t="s">
         <v>106</v>
       </c>
@@ -8373,7 +8408,7 @@
       <c r="AH52" s="13"/>
       <c r="AI52" s="13"/>
     </row>
-    <row r="53" spans="3:35">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C53" s="2" t="s">
         <v>107</v>
       </c>
@@ -8460,7 +8495,7 @@
       <c r="AH53" s="13"/>
       <c r="AI53" s="13"/>
     </row>
-    <row r="54" spans="3:35">
+    <row r="54" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C54" s="2" t="s">
         <v>108</v>
       </c>
@@ -8547,7 +8582,7 @@
       <c r="AH54" s="13"/>
       <c r="AI54" s="13"/>
     </row>
-    <row r="55" spans="3:35">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C55" s="2" t="s">
         <v>109</v>
       </c>
@@ -8634,7 +8669,7 @@
       <c r="AH55" s="13"/>
       <c r="AI55" s="13"/>
     </row>
-    <row r="56" spans="3:35">
+    <row r="56" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C56" s="2" t="s">
         <v>110</v>
       </c>
@@ -8721,7 +8756,7 @@
       <c r="AH56" s="13"/>
       <c r="AI56" s="13"/>
     </row>
-    <row r="57" spans="3:35">
+    <row r="57" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C57" s="11" t="s">
         <v>111</v>
       </c>
@@ -8833,7 +8868,7 @@
       <c r="AH57" s="13"/>
       <c r="AI57" s="13"/>
     </row>
-    <row r="58" spans="3:35">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C58" s="1" t="s">
         <v>112</v>
       </c>
@@ -8945,7 +8980,7 @@
       <c r="AH58" s="13"/>
       <c r="AI58" s="13"/>
     </row>
-    <row r="59" spans="3:35">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.25">
       <c r="D59" s="13"/>
       <c r="E59" s="15"/>
       <c r="F59" s="15"/>
@@ -8959,7 +8994,7 @@
       <c r="N59" s="15"/>
       <c r="O59" s="11"/>
     </row>
-    <row r="60" spans="3:35">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C60" s="3" t="s">
         <v>114</v>
       </c>
@@ -8975,7 +9010,7 @@
       <c r="M60" s="13"/>
       <c r="N60" s="13"/>
     </row>
-    <row r="61" spans="3:35">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C61" s="2" t="s">
         <v>58</v>
       </c>
@@ -9084,7 +9119,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="62" spans="3:35">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C62" s="2" t="s">
         <v>59</v>
       </c>
@@ -9166,7 +9201,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="63" spans="3:35">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C63" s="2" t="s">
         <v>60</v>
       </c>
@@ -9248,7 +9283,7 @@
         <v>-571</v>
       </c>
     </row>
-    <row r="64" spans="3:35">
+    <row r="64" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C64" s="2" t="s">
         <v>61</v>
       </c>
@@ -9330,7 +9365,7 @@
         <v>-9</v>
       </c>
     </row>
-    <row r="65" spans="3:32">
+    <row r="65" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C65" s="2" t="s">
         <v>62</v>
       </c>
@@ -9412,7 +9447,7 @@
         <v>-35</v>
       </c>
     </row>
-    <row r="66" spans="3:32">
+    <row r="66" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C66" s="2" t="s">
         <v>47</v>
       </c>
@@ -9494,7 +9529,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="67" spans="3:32">
+    <row r="67" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C67" s="2" t="s">
         <v>63</v>
       </c>
@@ -9576,7 +9611,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="3:32">
+    <row r="68" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C68" s="2" t="s">
         <v>64</v>
       </c>
@@ -9679,7 +9714,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="69" spans="3:32">
+    <row r="69" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C69" s="2" t="s">
         <v>65</v>
       </c>
@@ -9761,7 +9796,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="70" spans="3:32">
+    <row r="70" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C70" s="1" t="s">
         <v>31</v>
       </c>
@@ -9870,11 +9905,11 @@
         <v>219</v>
       </c>
     </row>
-    <row r="71" spans="3:32">
+    <row r="71" spans="3:32" x14ac:dyDescent="0.25">
       <c r="W71" s="13"/>
       <c r="X71" s="13"/>
     </row>
-    <row r="72" spans="3:32">
+    <row r="72" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C72" s="2" t="s">
         <v>66</v>
       </c>
@@ -9956,7 +9991,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="73" spans="3:32">
+    <row r="73" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C73" s="2" t="s">
         <v>67</v>
       </c>
@@ -10038,7 +10073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="3:32">
+    <row r="74" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C74" s="2" t="s">
         <v>68</v>
       </c>
@@ -10120,7 +10155,7 @@
         <v>-75</v>
       </c>
     </row>
-    <row r="75" spans="3:32">
+    <row r="75" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C75" s="2" t="s">
         <v>69</v>
       </c>
@@ -10199,7 +10234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="3:32">
+    <row r="76" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C76" s="2" t="s">
         <v>70</v>
       </c>
@@ -10281,7 +10316,7 @@
         <v>-53</v>
       </c>
     </row>
-    <row r="77" spans="3:32">
+    <row r="77" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C77" s="2" t="s">
         <v>71</v>
       </c>
@@ -10363,7 +10398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="3:32">
+    <row r="78" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C78" s="2" t="s">
         <v>72</v>
       </c>
@@ -10445,7 +10480,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="79" spans="3:32">
+    <row r="79" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C79" s="2" t="s">
         <v>73</v>
       </c>
@@ -10527,7 +10562,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="80" spans="3:32">
+    <row r="80" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C80" s="2" t="s">
         <v>169</v>
       </c>
@@ -10609,7 +10644,7 @@
         <v>-264</v>
       </c>
     </row>
-    <row r="81" spans="3:32">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C81" s="2" t="s">
         <v>85</v>
       </c>
@@ -10691,7 +10726,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="3:32">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C82" s="2" t="s">
         <v>74</v>
       </c>
@@ -10773,7 +10808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="3:32">
+    <row r="83" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C83" s="1" t="s">
         <v>33</v>
       </c>
@@ -10882,11 +10917,11 @@
         <v>164</v>
       </c>
     </row>
-    <row r="84" spans="3:32">
+    <row r="84" spans="3:32" x14ac:dyDescent="0.25">
       <c r="W84" s="13"/>
       <c r="X84" s="13"/>
     </row>
-    <row r="85" spans="3:32">
+    <row r="85" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C85" s="2" t="s">
         <v>75</v>
       </c>
@@ -10968,7 +11003,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="86" spans="3:32">
+    <row r="86" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C86" s="2" t="s">
         <v>76</v>
       </c>
@@ -11050,7 +11085,7 @@
         <v>-122</v>
       </c>
     </row>
-    <row r="87" spans="3:32">
+    <row r="87" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C87" s="2" t="s">
         <v>77</v>
       </c>
@@ -11132,7 +11167,7 @@
         <v>-38</v>
       </c>
     </row>
-    <row r="88" spans="3:32">
+    <row r="88" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C88" s="2" t="s">
         <v>78</v>
       </c>
@@ -11214,7 +11249,7 @@
         <v>-19</v>
       </c>
     </row>
-    <row r="89" spans="3:32">
+    <row r="89" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C89" s="2" t="s">
         <v>79</v>
       </c>
@@ -11293,7 +11328,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="3:32">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C90" s="2" t="s">
         <v>80</v>
       </c>
@@ -11375,7 +11410,7 @@
         <v>-127</v>
       </c>
     </row>
-    <row r="91" spans="3:32">
+    <row r="91" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C91" s="2" t="s">
         <v>81</v>
       </c>
@@ -11454,7 +11489,7 @@
         <v>-33</v>
       </c>
     </row>
-    <row r="92" spans="3:32">
+    <row r="92" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C92" s="2" t="s">
         <v>82</v>
       </c>
@@ -11536,7 +11571,7 @@
         <v>-82</v>
       </c>
     </row>
-    <row r="93" spans="3:32">
+    <row r="93" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C93" s="1" t="s">
         <v>32</v>
       </c>
@@ -11645,11 +11680,11 @@
         <v>-344</v>
       </c>
     </row>
-    <row r="94" spans="3:32">
+    <row r="94" spans="3:32" x14ac:dyDescent="0.25">
       <c r="W94" s="13"/>
       <c r="X94" s="13"/>
     </row>
-    <row r="95" spans="3:32">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C95" s="2" t="s">
         <v>83</v>
       </c>
@@ -11756,11 +11791,11 @@
         <v>39</v>
       </c>
     </row>
-    <row r="96" spans="3:32">
+    <row r="96" spans="3:32" x14ac:dyDescent="0.25">
       <c r="W96" s="13"/>
       <c r="X96" s="13"/>
     </row>
-    <row r="97" spans="3:32">
+    <row r="97" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C97" s="2" t="s">
         <v>84</v>
       </c>
@@ -11877,7 +11912,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{249058E0-3BA5-6740-BE74-082DF7085DA4}">
   <dimension ref="B3:AA56"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.6640625" style="2" customWidth="1"/>
     <col min="2" max="2" width="46" style="2" customWidth="1"/>
@@ -11893,12 +11928,12 @@
     <col min="28" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:27">
+    <row r="3" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="2:27">
+    <row r="4" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B4" s="31"/>
       <c r="C4" s="42" t="s">
         <v>3</v>
@@ -11976,7 +12011,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="5" spans="2:27">
+    <row r="5" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B5" s="44" t="s">
         <v>134</v>
       </c>
@@ -11986,7 +12021,7 @@
       <c r="V5" s="49"/>
       <c r="AA5" s="49"/>
     </row>
-    <row r="6" spans="2:27">
+    <row r="6" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>42</v>
       </c>
@@ -12067,7 +12102,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="7" spans="2:27">
+    <row r="7" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
         <v>189</v>
       </c>
@@ -12157,7 +12192,7 @@
         <v>-0.48101265822784811</v>
       </c>
     </row>
-    <row r="8" spans="2:27">
+    <row r="8" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B8" s="39" t="s">
         <v>146</v>
       </c>
@@ -12238,7 +12273,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="9" spans="2:27">
+    <row r="9" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B9" s="39" t="s">
         <v>147</v>
       </c>
@@ -12319,7 +12354,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="2:27">
+    <row r="10" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B10" s="39" t="s">
         <v>144</v>
       </c>
@@ -12400,7 +12435,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="2:27">
+    <row r="11" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B11" s="40" t="s">
         <v>135</v>
       </c>
@@ -12481,7 +12516,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="2:27">
+    <row r="12" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B12" s="45" t="s">
         <v>130</v>
       </c>
@@ -12562,7 +12597,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="2:27">
+    <row r="13" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B13" s="40" t="s">
         <v>136</v>
       </c>
@@ -12643,7 +12678,7 @@
         <v>0.1574279379157428</v>
       </c>
     </row>
-    <row r="14" spans="2:27">
+    <row r="14" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B14" s="45" t="s">
         <v>137</v>
       </c>
@@ -12724,7 +12759,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="2:27">
+    <row r="15" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B15" s="39" t="s">
         <v>30</v>
       </c>
@@ -12805,7 +12840,7 @@
         <v>0.12195121951219512</v>
       </c>
     </row>
-    <row r="16" spans="2:27">
+    <row r="16" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B16" s="37" t="s">
         <v>138</v>
       </c>
@@ -12884,7 +12919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:27">
+    <row r="17" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>143</v>
       </c>
@@ -12963,7 +12998,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="18" spans="2:27">
+    <row r="18" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B18" s="31" t="s">
         <v>139</v>
       </c>
@@ -13044,7 +13079,7 @@
         <v>-12</v>
       </c>
     </row>
-    <row r="19" spans="2:27">
+    <row r="19" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
         <v>140</v>
       </c>
@@ -13125,7 +13160,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="2:27">
+    <row r="20" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B20" s="39" t="s">
         <v>141</v>
       </c>
@@ -13206,14 +13241,14 @@
         <v>9.0909090909090912E-2</v>
       </c>
     </row>
-    <row r="21" spans="2:27">
+    <row r="21" spans="2:27" x14ac:dyDescent="0.25">
       <c r="G21" s="49"/>
       <c r="L21" s="49"/>
       <c r="Q21" s="49"/>
       <c r="V21" s="49"/>
       <c r="AA21" s="49"/>
     </row>
-    <row r="22" spans="2:27">
+    <row r="22" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B22" s="44" t="s">
         <v>142</v>
       </c>
@@ -13223,7 +13258,7 @@
       <c r="V22" s="49"/>
       <c r="AA22" s="49"/>
     </row>
-    <row r="23" spans="2:27">
+    <row r="23" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>42</v>
       </c>
@@ -13304,7 +13339,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="24" spans="2:27">
+    <row r="24" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B24" s="11" t="s">
         <v>189</v>
       </c>
@@ -13394,7 +13429,7 @@
         <v>-0.51117318435754189</v>
       </c>
     </row>
-    <row r="25" spans="2:27">
+    <row r="25" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B25" s="39" t="s">
         <v>148</v>
       </c>
@@ -13475,7 +13510,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="26" spans="2:27">
+    <row r="26" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B26" s="40" t="s">
         <v>135</v>
       </c>
@@ -13556,7 +13591,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="2:27">
+    <row r="27" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B27" s="45" t="s">
         <v>130</v>
       </c>
@@ -13637,7 +13672,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="2:27">
+    <row r="28" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B28" s="40" t="s">
         <v>136</v>
       </c>
@@ -13718,7 +13753,7 @@
         <v>0.26285714285714284</v>
       </c>
     </row>
-    <row r="29" spans="2:27">
+    <row r="29" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B29" s="45" t="s">
         <v>137</v>
       </c>
@@ -13799,7 +13834,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="2:27">
+    <row r="30" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B30" s="39" t="s">
         <v>30</v>
       </c>
@@ -13880,7 +13915,7 @@
         <v>0.13714285714285715</v>
       </c>
     </row>
-    <row r="31" spans="2:27">
+    <row r="31" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B31" s="37" t="s">
         <v>138</v>
       </c>
@@ -13959,7 +13994,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="2:27">
+    <row r="32" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B32" s="39" t="s">
         <v>148</v>
       </c>
@@ -14023,7 +14058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:27">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B33" s="39" t="s">
         <v>135</v>
       </c>
@@ -14087,7 +14122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:27">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
         <v>143</v>
       </c>
@@ -14166,7 +14201,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="35" spans="2:27">
+    <row r="35" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B35" s="31" t="s">
         <v>139</v>
       </c>
@@ -14247,7 +14282,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="36" spans="2:27">
+    <row r="36" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
         <v>140</v>
       </c>
@@ -14328,7 +14363,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="2:27">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B37" s="39" t="s">
         <v>141</v>
       </c>
@@ -14409,14 +14444,14 @@
         <v>0.29714285714285715</v>
       </c>
     </row>
-    <row r="38" spans="2:27">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.25">
       <c r="G38" s="49"/>
       <c r="L38" s="49"/>
       <c r="Q38" s="49"/>
       <c r="V38" s="49"/>
       <c r="AA38" s="49"/>
     </row>
-    <row r="39" spans="2:27">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B39" s="44" t="s">
         <v>150</v>
       </c>
@@ -14426,7 +14461,7 @@
       <c r="V39" s="49"/>
       <c r="AA39" s="49"/>
     </row>
-    <row r="40" spans="2:27">
+    <row r="40" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B40" s="1" t="s">
         <v>42</v>
       </c>
@@ -14507,7 +14542,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="2:27">
+    <row r="41" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B41" s="11" t="s">
         <v>189</v>
       </c>
@@ -14597,7 +14632,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="42" spans="2:27">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B42" s="39" t="s">
         <v>151</v>
       </c>
@@ -14678,7 +14713,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="2:27">
+    <row r="43" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B43" s="40" t="s">
         <v>152</v>
       </c>
@@ -14759,7 +14794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:27">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B44" s="45" t="s">
         <v>130</v>
       </c>
@@ -14840,7 +14875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:27">
+    <row r="45" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B45" s="45" t="s">
         <v>137</v>
       </c>
@@ -14921,7 +14956,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="46" spans="2:27">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B46" s="46" t="s">
         <v>138</v>
       </c>
@@ -15002,7 +15037,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="47" spans="2:27">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B47" s="39" t="s">
         <v>153</v>
       </c>
@@ -15083,7 +15118,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="48" spans="2:27">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B48" s="39" t="s">
         <v>154</v>
       </c>
@@ -15164,7 +15199,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="49" spans="2:27">
+    <row r="49" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B49" s="40" t="s">
         <v>155</v>
       </c>
@@ -15245,7 +15280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:27">
+    <row r="50" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B50" s="45" t="s">
         <v>61</v>
       </c>
@@ -15326,7 +15361,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="2:27">
+    <row r="51" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B51" s="1" t="s">
         <v>156</v>
       </c>
@@ -15407,7 +15442,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="52" spans="2:27">
+    <row r="52" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B52" s="39" t="s">
         <v>157</v>
       </c>
@@ -15488,7 +15523,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="2:27">
+    <row r="53" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B53" s="39" t="s">
         <v>158</v>
       </c>
@@ -15569,7 +15604,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="2:27">
+    <row r="54" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B54" s="40" t="s">
         <v>159</v>
       </c>
@@ -15650,7 +15685,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="2:27">
+    <row r="55" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B55" s="2" t="s">
         <v>139</v>
       </c>
@@ -15729,7 +15764,7 @@
         <v>-9</v>
       </c>
     </row>
-    <row r="56" spans="2:27">
+    <row r="56" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
         <v>160</v>
       </c>
@@ -15823,7 +15858,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D96005A-D926-0A4A-83BB-6287EB4C1EBD}">
   <dimension ref="A2:G104"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="34"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="34" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="47.1640625" style="63" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" style="63" bestFit="1" customWidth="1"/>
@@ -15835,25 +15870,25 @@
     <col min="8" max="16384" width="10.83203125" style="63"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B2" s="64"/>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="65" t="s">
         <v>123</v>
       </c>
       <c r="B4" s="64">
         <f>Modell!B4/SOTP!G26</f>
-        <v>0.59774246807432097</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>0.6420850589426671</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="65"/>
       <c r="B5" s="65"/>
       <c r="C5" s="65"/>
       <c r="D5" s="65"/>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="66" t="s">
         <v>170</v>
       </c>
@@ -15874,7 +15909,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="63" t="s">
         <v>188</v>
       </c>
@@ -15896,7 +15931,7 @@
         <v>298.34006280843425</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" s="63" t="s">
         <v>132</v>
       </c>
@@ -15918,7 +15953,7 @@
         <v>235.26244952893674</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" s="69" t="s">
         <v>131</v>
       </c>
@@ -15941,7 +15976,7 @@
         <v>-10.228802153432031</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" s="65" t="s">
         <v>133</v>
       </c>
@@ -15955,10 +15990,10 @@
         <v>523.3737101839389</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="G12" s="68"/>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A13" s="73" t="s">
         <v>195</v>
       </c>
@@ -15979,7 +16014,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14" s="63" t="s">
         <v>172</v>
       </c>
@@ -15987,21 +16022,21 @@
         <v>160210000</v>
       </c>
       <c r="D14" s="63">
-        <v>168.9</v>
+        <v>182.5</v>
       </c>
       <c r="E14" s="63">
         <v>1</v>
       </c>
       <c r="F14" s="67">
         <f>B14*D14</f>
-        <v>27059469000</v>
+        <v>29238325000</v>
       </c>
       <c r="G14" s="68">
         <f>F14/$B$26</f>
-        <v>606.98674293405111</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>655.86193360251229</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A15" s="63" t="s">
         <v>173</v>
       </c>
@@ -16009,22 +16044,22 @@
         <v>8250000</v>
       </c>
       <c r="D15" s="67">
-        <v>203000</v>
+        <v>196900</v>
       </c>
       <c r="E15" s="63">
         <f>B30</f>
-        <v>6.6E-3</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="F15" s="67">
         <f>(B15*D15)*E15</f>
-        <v>11053350000</v>
+        <v>11370975000</v>
       </c>
       <c r="G15" s="68">
         <f>F15/$B$26</f>
-        <v>247.94414535666218</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>255.06897711978465</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16" s="63" t="s">
         <v>174</v>
       </c>
@@ -16032,21 +16067,21 @@
         <v>96844009</v>
       </c>
       <c r="D16" s="63">
-        <v>6.29</v>
+        <v>6.6</v>
       </c>
       <c r="E16" s="63">
         <v>1</v>
       </c>
       <c r="F16" s="67">
         <f>(B16*D16)</f>
-        <v>609148816.61000001</v>
+        <v>639170459.39999998</v>
       </c>
       <c r="G16" s="68">
         <f>F16/$B$26</f>
-        <v>13.664172647151188</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>14.337605639300135</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A17" s="65" t="s">
         <v>133</v>
       </c>
@@ -16057,10 +16092,10 @@
       <c r="F17" s="65"/>
       <c r="G17" s="72">
         <f>SUM(G14:G16)</f>
-        <v>868.59506093786445</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>925.26851636159711</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A19" s="74" t="s">
         <v>175</v>
       </c>
@@ -16075,7 +16110,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
       <c r="D20" s="67"/>
       <c r="F20" s="67">
         <f>Modell!B7*1000000</f>
@@ -16086,7 +16121,7 @@
         <v>57.720951099147598</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A22" s="76" t="s">
         <v>96</v>
       </c>
@@ -16101,7 +16136,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="D23" s="67">
         <v>864500000</v>
       </c>
@@ -16114,7 +16149,7 @@
         <v>77.731493943472415</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A25" s="78" t="s">
         <v>133</v>
       </c>
@@ -16128,47 +16163,47 @@
         <v>179</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="42" customHeight="1">
+    <row r="26" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="79"/>
       <c r="B26" s="80">
         <v>44580000</v>
       </c>
       <c r="F26" s="67">
         <f>SUM(F8:F10)+SUM(F14:F16)-F20+F23</f>
-        <v>62946037816.610001</v>
+        <v>65472540459.400002</v>
       </c>
       <c r="G26" s="81">
         <f>F26/B26</f>
-        <v>1411.9793139661283</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>1468.6527693898609</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A27" s="79"/>
       <c r="B27" s="79"/>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A28" s="78" t="s">
         <v>183</v>
       </c>
       <c r="B28" s="79"/>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A29" s="79" t="s">
         <v>57</v>
       </c>
       <c r="B29" s="79">
-        <v>9.69</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>9.51</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A30" s="79" t="s">
         <v>184</v>
       </c>
       <c r="B30" s="79">
-        <v>6.6E-3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A31" s="79" t="s">
         <v>185</v>
       </c>
@@ -16176,7 +16211,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A91" s="63" t="s">
         <v>188</v>
       </c>
@@ -16185,7 +16220,7 @@
         <v>298.34006280843425</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A92" s="63" t="s">
         <v>132</v>
       </c>
@@ -16194,7 +16229,7 @@
         <v>235.26244952893674</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A93" s="69" t="s">
         <v>131</v>
       </c>
@@ -16203,7 +16238,7 @@
         <v>-10.228802153432031</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A94" s="65" t="s">
         <v>170</v>
       </c>
@@ -16212,43 +16247,43 @@
         <v>523.3737101839389</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A96" s="63" t="s">
         <v>172</v>
       </c>
       <c r="B96" s="68">
         <f>G14</f>
-        <v>606.98674293405111</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2">
+        <v>655.86193360251229</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A97" s="63" t="s">
         <v>173</v>
       </c>
       <c r="B97" s="68">
         <f>G15</f>
-        <v>247.94414535666218</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2">
+        <v>255.06897711978465</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A98" s="63" t="s">
         <v>174</v>
       </c>
       <c r="B98" s="68">
         <f>G16</f>
-        <v>13.664172647151188</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2">
+        <v>14.337605639300135</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A99" s="65" t="s">
         <v>171</v>
       </c>
       <c r="B99" s="72">
         <f>SUM(B96:B98)</f>
-        <v>868.59506093786445</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2">
+        <v>925.26851636159711</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A101" s="63" t="s">
         <v>175</v>
       </c>
@@ -16257,7 +16292,7 @@
         <v>-57.720951099147598</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A102" s="63" t="s">
         <v>96</v>
       </c>
@@ -16266,13 +16301,13 @@
         <v>77.731493943472415</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A104" s="63" t="s">
         <v>133</v>
       </c>
       <c r="B104" s="68">
         <f>B94+B99+B101+B102</f>
-        <v>1411.9793139661283</v>
+        <v>1468.6527693898609</v>
       </c>
     </row>
   </sheetData>
@@ -16285,13 +16320,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEC8E745-DC06-8448-81B5-DC40131426CF}">
   <dimension ref="C4:F6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="29.5" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="28.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:6" ht="62">
+    <row r="4" spans="3:6" ht="62" x14ac:dyDescent="0.7">
       <c r="C4" s="30"/>
       <c r="D4" s="30">
         <v>2026</v>
@@ -16303,38 +16338,38 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="5" spans="3:6" ht="62">
+    <row r="5" spans="3:6" ht="62" x14ac:dyDescent="0.7">
       <c r="C5" s="30" t="s">
         <v>34</v>
       </c>
       <c r="D5" s="35">
         <f>Modell!$B$9/(Modell!AG11*Modell!$B$11)</f>
-        <v>29.211906494193244</v>
+        <v>32.635912661007239</v>
       </c>
       <c r="E5" s="35">
         <f>Modell!$B$9/(Modell!AH11*Modell!$B$11)</f>
-        <v>28.088371629031972</v>
+        <v>31.380685250968504</v>
       </c>
       <c r="F5" s="35">
         <f>Modell!$B$9/(Modell!AI11*Modell!$B$11)</f>
-        <v>27.008049643299984</v>
-      </c>
-    </row>
-    <row r="6" spans="3:6" ht="62">
+        <v>30.173735818238956</v>
+      </c>
+    </row>
+    <row r="6" spans="3:6" ht="62" x14ac:dyDescent="0.7">
       <c r="C6" s="30" t="s">
         <v>35</v>
       </c>
       <c r="D6" s="35">
         <f>Modell!$B$4/Modell!AG19</f>
-        <v>7.6681680762827025</v>
+        <v>8.5676332890220248</v>
       </c>
       <c r="E6" s="35">
         <f>Modell!$B$4/Modell!AH19</f>
-        <v>7.8853274679905674</v>
+        <v>8.810265168619793</v>
       </c>
       <c r="F6" s="35">
         <f>Modell!$B$4/Modell!AI19</f>
-        <v>8.0956505003212502</v>
+        <v>9.0452587936053774</v>
       </c>
     </row>
   </sheetData>
